--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -285,7 +285,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="115">
   <si>
     <t>#</t>
   </si>
@@ -627,6 +627,9 @@
   </si>
   <si>
     <t>击杀{0}个怪物，福利5（彼此）</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物，福利6（ci）</t>
   </si>
 </sst>
 </file>
@@ -5703,7 +5706,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R73"/>
+  <dimension ref="A1:R76"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -9107,6 +9110,147 @@
       </c>
       <c r="Q73" s="1">
         <v>68</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:18">
+      <c r="C74" s="1">
+        <v>3069</v>
+      </c>
+      <c r="D74" s="1">
+        <v>3</v>
+      </c>
+      <c r="E74" s="1">
+        <v>3</v>
+      </c>
+      <c r="F74" s="1">
+        <v>1</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0</v>
+      </c>
+      <c r="H74" s="1">
+        <v>301</v>
+      </c>
+      <c r="I74" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J74" s="1">
+        <v>0</v>
+      </c>
+      <c r="K74" s="1">
+        <v>0</v>
+      </c>
+      <c r="L74" s="1">
+        <v>5</v>
+      </c>
+      <c r="M74" s="1">
+        <v>5001</v>
+      </c>
+      <c r="N74" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O74" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="P74" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q74" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:18">
+      <c r="C75" s="1">
+        <v>3070</v>
+      </c>
+      <c r="D75" s="1">
+        <v>3</v>
+      </c>
+      <c r="E75" s="1">
+        <v>3</v>
+      </c>
+      <c r="F75" s="1">
+        <v>1</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0</v>
+      </c>
+      <c r="H75" s="1">
+        <v>301</v>
+      </c>
+      <c r="I75" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J75" s="1">
+        <v>0</v>
+      </c>
+      <c r="K75" s="1">
+        <v>0</v>
+      </c>
+      <c r="L75" s="1">
+        <v>5</v>
+      </c>
+      <c r="M75" s="1">
+        <v>5002</v>
+      </c>
+      <c r="N75" s="1">
+        <v>1000</v>
+      </c>
+      <c r="O75" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="P75" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q75" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:18">
+      <c r="C76" s="1">
+        <v>3071</v>
+      </c>
+      <c r="D76" s="1">
+        <v>3</v>
+      </c>
+      <c r="E76" s="1">
+        <v>3</v>
+      </c>
+      <c r="F76" s="1">
+        <v>1</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0</v>
+      </c>
+      <c r="H76" s="1">
+        <v>301</v>
+      </c>
+      <c r="I76" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J76" s="1">
+        <v>0</v>
+      </c>
+      <c r="K76" s="1">
+        <v>0</v>
+      </c>
+      <c r="L76" s="1">
+        <v>8</v>
+      </c>
+      <c r="M76" s="1">
+        <v>11</v>
+      </c>
+      <c r="N76" s="1">
+        <v>200</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="P76" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q76" s="1">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -10623,26 +10767,101 @@
       <c r="R25" s="2"/>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C26" s="1">
+        <v>12021</v>
+      </c>
+      <c r="D26" s="1">
+        <v>12</v>
+      </c>
+      <c r="E26" s="1">
+        <v>12</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1">
+        <v>1</v>
+      </c>
+      <c r="H26" s="1">
+        <v>301</v>
+      </c>
+      <c r="I26" s="1">
+        <v>50000</v>
+      </c>
+      <c r="J26" s="1">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M26" s="1">
+        <v>1</v>
+      </c>
+      <c r="N26" s="1">
+        <v>0</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>21</v>
+      </c>
       <c r="R26" s="2"/>
     </row>
     <row r="27" customFormat="1" customHeight="1" spans="1:18">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
+      <c r="C27" s="1">
+        <v>12022</v>
+      </c>
+      <c r="D27" s="1">
+        <v>12</v>
+      </c>
+      <c r="E27" s="1">
+        <v>12</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1">
+        <v>301</v>
+      </c>
+      <c r="I27" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M27" s="1">
+        <v>1</v>
+      </c>
+      <c r="N27" s="1">
+        <v>0</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>22</v>
+      </c>
       <c r="R27" s="2"/>
     </row>
     <row r="28" customFormat="1" customHeight="1" spans="1:18">
@@ -10693,7 +10912,7 @@
     <row r="57" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="R24 R25 R6:R23 R26:R27 C3:R5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="R6:R27 C3:R5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -285,7 +285,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="116">
   <si>
     <t>#</t>
   </si>
@@ -630,6 +630,9 @@
   </si>
   <si>
     <t>击杀{0}个怪物，福利6（ci）</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物，福利7（Z）</t>
   </si>
 </sst>
 </file>
@@ -808,12 +811,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -10865,23 +10868,99 @@
       <c r="R27" s="2"/>
     </row>
     <row r="28" customFormat="1" customHeight="1" spans="1:18">
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
-    </row>
-    <row r="29" customFormat="1" customHeight="1"/>
+      <c r="C28" s="1">
+        <v>12023</v>
+      </c>
+      <c r="D28" s="1">
+        <v>12</v>
+      </c>
+      <c r="E28" s="1">
+        <v>12</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1">
+        <v>1</v>
+      </c>
+      <c r="H28" s="1">
+        <v>301</v>
+      </c>
+      <c r="I28" s="1">
+        <v>50000</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M28" s="1">
+        <v>1</v>
+      </c>
+      <c r="N28" s="1">
+        <v>0</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="P28" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C29" s="1">
+        <v>12024</v>
+      </c>
+      <c r="D29" s="1">
+        <v>12</v>
+      </c>
+      <c r="E29" s="1">
+        <v>12</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1">
+        <v>301</v>
+      </c>
+      <c r="I29" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M29" s="1">
+        <v>1</v>
+      </c>
+      <c r="N29" s="1">
+        <v>0</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>24</v>
+      </c>
+    </row>
     <row r="30" customFormat="1" customHeight="1"/>
     <row r="31" customFormat="1" customHeight="1"/>
     <row r="32" customFormat="1" customHeight="1"/>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="新入世界" sheetId="1" r:id="rId1"/>
@@ -17,6 +17,7 @@
     <sheet name="初露锋芒" sheetId="3" r:id="rId3"/>
     <sheet name="每日任务" sheetId="4" r:id="rId4"/>
     <sheet name="福利任务" sheetId="6" r:id="rId5"/>
+    <sheet name="节日任务" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -284,8 +285,44 @@
 </comments>
 </file>
 
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="R3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 闯关层数
+2 穿戴装备
+3 强化装备
+4 挑战副本
+5 设置回收</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="119">
   <si>
     <t>#</t>
   </si>
@@ -633,6 +670,15 @@
   </si>
   <si>
     <t>击杀{0}个怪物，福利7（Z）</t>
+  </si>
+  <si>
+    <t>奖励5个银沙挂坠</t>
+  </si>
+  <si>
+    <t>奖励5个回光护手</t>
+  </si>
+  <si>
+    <t>奖励5个流风长剑</t>
   </si>
 </sst>
 </file>
@@ -811,12 +857,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -10999,4 +11045,457 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:R57"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="7" width="11.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5833333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.8333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.4166666666667" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5" style="1" customWidth="1"/>
+    <col min="13" max="14" width="13.75" style="1" customWidth="1"/>
+    <col min="15" max="15" width="42.75" style="1" customWidth="1"/>
+    <col min="16" max="16" width="21.4166666666667" style="1" customWidth="1"/>
+    <col min="17" max="17" width="19.625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5833333333333" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="2">
+        <v>5</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R4" s="2"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R5" s="2"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C6" s="1">
+        <v>13001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1">
+        <v>13</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>301</v>
+      </c>
+      <c r="I6" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>1</v>
+      </c>
+      <c r="R6" s="2"/>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C7" s="1">
+        <v>13002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>13</v>
+      </c>
+      <c r="E7" s="1">
+        <v>13</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1">
+        <v>301</v>
+      </c>
+      <c r="I7" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>2</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C8" s="1">
+        <v>13003</v>
+      </c>
+      <c r="D8" s="1">
+        <v>13</v>
+      </c>
+      <c r="E8" s="1">
+        <v>13</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <v>301</v>
+      </c>
+      <c r="I8" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>3</v>
+      </c>
+      <c r="R8" s="2"/>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R9" s="2"/>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R10" s="2"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R11" s="2"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R12" s="2"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R13" s="2"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R14" s="2"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R15" s="2"/>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R16" s="2"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R17" s="2"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R18" s="2"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R19" s="2"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R20" s="2"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R21" s="2"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R22" s="2"/>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R23" s="2"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R24" s="2"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R25" s="2"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R26" s="2"/>
+    </row>
+    <row r="27" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="2"/>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+    </row>
+    <row r="29" customFormat="1" customHeight="1"/>
+    <row r="30" customFormat="1" customHeight="1"/>
+    <row r="31" customFormat="1" customHeight="1"/>
+    <row r="32" customFormat="1" customHeight="1"/>
+    <row r="33" customFormat="1" customHeight="1"/>
+    <row r="34" customFormat="1" customHeight="1"/>
+    <row r="35" customFormat="1" customHeight="1"/>
+    <row r="36" customFormat="1" customHeight="1"/>
+    <row r="37" customFormat="1" customHeight="1"/>
+    <row r="38" customFormat="1" customHeight="1"/>
+    <row r="39" customFormat="1" customHeight="1"/>
+    <row r="40" customFormat="1" customHeight="1"/>
+    <row r="41" customFormat="1" customHeight="1"/>
+    <row r="42" customFormat="1" customHeight="1"/>
+    <row r="43" customFormat="1" customHeight="1"/>
+    <row r="44" customFormat="1" customHeight="1"/>
+    <row r="45" customFormat="1" customHeight="1"/>
+    <row r="46" customFormat="1" customHeight="1"/>
+    <row r="47" customFormat="1" customHeight="1"/>
+    <row r="48" customFormat="1" customHeight="1"/>
+    <row r="49" customFormat="1" customHeight="1"/>
+    <row r="50" customFormat="1" customHeight="1"/>
+    <row r="51" customFormat="1" customHeight="1"/>
+    <row r="52" customFormat="1" customHeight="1"/>
+    <row r="53" customFormat="1" customHeight="1"/>
+    <row r="54" customFormat="1" customHeight="1"/>
+    <row r="55" customFormat="1" customHeight="1"/>
+    <row r="56" customFormat="1" customHeight="1"/>
+    <row r="57" customFormat="1" customHeight="1"/>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="R6:R27 C3:R5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -672,13 +672,13 @@
     <t>击杀{0}个怪物，福利7（Z）</t>
   </si>
   <si>
-    <t>奖励5个银沙挂坠</t>
-  </si>
-  <si>
-    <t>奖励5个回光护手</t>
-  </si>
-  <si>
-    <t>奖励5个流风长剑</t>
+    <t>中秋活动，奖励5个银沙挂坠</t>
+  </si>
+  <si>
+    <t>中秋活动，奖励5个回光护手</t>
+  </si>
+  <si>
+    <t>中秋活动，奖励5个流风长剑</t>
   </si>
 </sst>
 </file>
@@ -857,12 +857,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="5"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="新入世界" sheetId="1" r:id="rId1"/>
@@ -857,12 +857,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1862,7 +1862,8 @@
         <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <f t="shared" ref="K6:K33" si="0">C6*10000</f>
+        <v>10000</v>
       </c>
       <c r="L6" s="1">
         <v>20</v>
@@ -1910,7 +1911,8 @@
         <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>20000</v>
       </c>
       <c r="L7" s="1">
         <v>20</v>
@@ -1958,7 +1960,8 @@
         <v>200000</v>
       </c>
       <c r="K8" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>30000</v>
       </c>
       <c r="L8" s="1">
         <v>5</v>
@@ -2006,7 +2009,8 @@
         <v>200000</v>
       </c>
       <c r="K9" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>40000</v>
       </c>
       <c r="L9" s="1">
         <v>5</v>
@@ -2054,7 +2058,8 @@
         <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>50000</v>
       </c>
       <c r="L10" s="1">
         <v>8</v>
@@ -2102,7 +2107,8 @@
         <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>60000</v>
       </c>
       <c r="L11" s="1">
         <v>8</v>
@@ -2150,7 +2156,8 @@
         <v>500000</v>
       </c>
       <c r="K12" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>70000</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -2198,7 +2205,8 @@
         <v>500000</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>80000</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -2246,7 +2254,8 @@
         <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>90000</v>
       </c>
       <c r="L14" s="1">
         <v>8</v>
@@ -2294,7 +2303,8 @@
         <v>500000</v>
       </c>
       <c r="K15" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>100000</v>
       </c>
       <c r="L15" s="1">
         <v>5</v>
@@ -2342,7 +2352,8 @@
         <v>1000000</v>
       </c>
       <c r="K16" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>110000</v>
       </c>
       <c r="L16" s="1">
         <v>5</v>
@@ -2390,7 +2401,8 @@
         <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>120000</v>
       </c>
       <c r="L17" s="1">
         <v>5</v>
@@ -2438,7 +2450,8 @@
         <v>1000000</v>
       </c>
       <c r="K18" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>130000</v>
       </c>
       <c r="L18" s="1">
         <v>5</v>
@@ -2486,7 +2499,8 @@
         <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>140000</v>
       </c>
       <c r="L19" s="1">
         <v>8</v>
@@ -2534,7 +2548,8 @@
         <v>1000000</v>
       </c>
       <c r="K20" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>150000</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
@@ -2582,7 +2597,8 @@
         <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>160000</v>
       </c>
       <c r="L21" s="1">
         <v>8</v>
@@ -2630,7 +2646,8 @@
         <v>1000000</v>
       </c>
       <c r="K22" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>170000</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
@@ -2678,7 +2695,8 @@
         <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>180000</v>
       </c>
       <c r="L23" s="1">
         <v>8</v>
@@ -2726,7 +2744,8 @@
         <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>190000</v>
       </c>
       <c r="L24" s="1">
         <v>8</v>
@@ -2774,7 +2793,8 @@
         <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>200000</v>
       </c>
       <c r="L25" s="1">
         <v>8</v>
@@ -2822,7 +2842,8 @@
         <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>210000</v>
       </c>
       <c r="L26" s="1">
         <v>8</v>
@@ -2872,7 +2893,8 @@
         <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>220000</v>
       </c>
       <c r="L27" s="1">
         <v>8</v>
@@ -2920,7 +2942,8 @@
         <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>230000</v>
       </c>
       <c r="L28" s="1">
         <v>8</v>
@@ -2967,7 +2990,8 @@
         <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>240000</v>
       </c>
       <c r="L29" s="1">
         <v>8</v>
@@ -3014,7 +3038,8 @@
         <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>250000</v>
       </c>
       <c r="L30" s="1">
         <v>8</v>
@@ -3061,7 +3086,8 @@
         <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>260000</v>
       </c>
       <c r="L31" s="1">
         <v>8</v>
@@ -3108,7 +3134,8 @@
         <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>270000</v>
       </c>
       <c r="L32" s="1">
         <v>8</v>
@@ -3155,7 +3182,8 @@
         <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>280000</v>
       </c>
       <c r="L33" s="1">
         <v>8</v>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="新入世界" sheetId="1" r:id="rId1"/>
@@ -322,7 +322,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="124">
   <si>
     <t>#</t>
   </si>
@@ -679,6 +679,21 @@
   </si>
   <si>
     <t>中秋活动，奖励5个流风长剑</t>
+  </si>
+  <si>
+    <t>10.1活动，奖励5个银沙挂坠</t>
+  </si>
+  <si>
+    <t>10.1活动，奖励5个回光护手</t>
+  </si>
+  <si>
+    <t>10.1活动，奖励5个流风长剑</t>
+  </si>
+  <si>
+    <t>10.1活动，奖励50次抽奖</t>
+  </si>
+  <si>
+    <t>10.1活动，奖励节日祝福图</t>
   </si>
 </sst>
 </file>
@@ -11397,18 +11412,243 @@
       <c r="R8" s="2"/>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C9" s="1">
+        <v>13004</v>
+      </c>
+      <c r="D9" s="1">
+        <v>13</v>
+      </c>
+      <c r="E9" s="1">
+        <v>13</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1">
+        <v>301</v>
+      </c>
+      <c r="I9" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>4</v>
+      </c>
       <c r="R9" s="2"/>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C10" s="1">
+        <v>13005</v>
+      </c>
+      <c r="D10" s="1">
+        <v>13</v>
+      </c>
+      <c r="E10" s="1">
+        <v>13</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1">
+        <v>301</v>
+      </c>
+      <c r="I10" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>5</v>
+      </c>
       <c r="R10" s="2"/>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C11" s="1">
+        <v>13006</v>
+      </c>
+      <c r="D11" s="1">
+        <v>13</v>
+      </c>
+      <c r="E11" s="1">
+        <v>13</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1">
+        <v>301</v>
+      </c>
+      <c r="I11" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>6</v>
+      </c>
       <c r="R11" s="2"/>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C12" s="1">
+        <v>13007</v>
+      </c>
+      <c r="D12" s="1">
+        <v>13</v>
+      </c>
+      <c r="E12" s="1">
+        <v>13</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1">
+        <v>301</v>
+      </c>
+      <c r="I12" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>7</v>
+      </c>
       <c r="R12" s="2"/>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C13" s="1">
+        <v>13008</v>
+      </c>
+      <c r="D13" s="1">
+        <v>13</v>
+      </c>
+      <c r="E13" s="1">
+        <v>13</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1">
+        <v>301</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>8</v>
+      </c>
       <c r="R13" s="2"/>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:18">
